--- a/xls/square_20_tri3_25.xlsx
+++ b/xls/square_20_tri3_25.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23">
+        <v>676</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23">
+        <v>441</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23">
+        <v>576</v>
+      </c>
+      <c r="G23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23">
+        <v>3174</v>
+      </c>
+      <c r="I23">
+        <v>1.427138755939261</v>
+      </c>
+      <c r="J23">
+        <v>-1.6667313505065142</v>
+      </c>
+      <c r="K23">
+        <v>2.292740435871059</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24">
+        <v>676</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24">
+        <v>441</v>
+      </c>
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24">
+        <v>625</v>
+      </c>
+      <c r="G24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24">
+        <v>3456</v>
+      </c>
+      <c r="I24">
+        <v>-0.27140677104354</v>
+      </c>
+      <c r="J24">
+        <v>-2.282240413461182</v>
+      </c>
+      <c r="K24">
+        <v>1.7243129434802265</v>
+      </c>
+    </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
         <v>11</v>
